--- a/Corte_3.xlsx
+++ b/Corte_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2026" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06C7060-CEE6-49C6-9C97-4BDA8C214187}"/>
+  <xr:revisionPtr revIDLastSave="2218" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{451BABDC-C44E-4DBA-A908-3311BF32A23F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -589,11 +589,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,6 +653,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1456,49 +1473,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
@@ -1507,40 +1524,40 @@
       <c r="S3" s="12"/>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.1</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="34"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="36"/>
       <c r="L6" s="3">
         <v>0.4</v>
       </c>
@@ -1550,13 +1567,13 @@
       <c r="N6" s="4">
         <v>0.5</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="37"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="39"/>
       <c r="T6" s="11" t="s">
         <v>13</v>
       </c>
@@ -1571,14 +1588,14 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -1622,14 +1639,14 @@
       <c r="W7" s="8"/>
     </row>
     <row r="8" spans="1:23">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="13"/>
       <c r="F8" s="1">
         <f>E8*0.1</f>
@@ -1672,14 +1689,14 @@
       </c>
     </row>
     <row r="9" spans="1:23">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="25" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="5"/>
       <c r="F9" s="1">
         <f>E9*0.1</f>
@@ -1722,14 +1739,14 @@
       </c>
     </row>
     <row r="10" spans="1:23">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="5"/>
       <c r="F10" s="1">
         <f>E10*0.1</f>
@@ -1772,14 +1789,14 @@
       </c>
     </row>
     <row r="11" spans="1:23">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="5"/>
       <c r="F11" s="1">
         <f>E11*0.1</f>
@@ -1822,14 +1839,14 @@
       </c>
     </row>
     <row r="12" spans="1:23">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="5"/>
       <c r="F12" s="1">
         <f>E12*0.1</f>
@@ -1872,14 +1889,14 @@
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="25" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="5"/>
       <c r="F13" s="1">
         <f>E13*0.1</f>
@@ -1922,14 +1939,14 @@
       </c>
     </row>
     <row r="14" spans="1:23">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="5"/>
       <c r="F14" s="1">
         <f>E14*0.1</f>
@@ -1972,14 +1989,14 @@
       </c>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="5"/>
       <c r="F15" s="1">
         <f>E15*0.1</f>
@@ -2022,14 +2039,14 @@
       </c>
     </row>
     <row r="16" spans="1:23">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="33"/>
+      <c r="C16" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="33"/>
       <c r="E16" s="5"/>
       <c r="F16" s="1">
         <f>E16*0.1</f>
@@ -2072,14 +2089,14 @@
       </c>
     </row>
     <row r="17" spans="1:23">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="26"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="5"/>
       <c r="F17" s="1">
         <f>E17*0.1</f>
@@ -2122,14 +2139,14 @@
       </c>
     </row>
     <row r="18" spans="1:23">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="25" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="5"/>
       <c r="F18" s="1">
         <f>E18*0.1</f>
@@ -2172,14 +2189,14 @@
       </c>
     </row>
     <row r="19" spans="1:23">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="25" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="5"/>
       <c r="F19" s="1">
         <f>E19*0.1</f>
@@ -2222,14 +2239,14 @@
       </c>
     </row>
     <row r="20" spans="1:23">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="25" t="s">
+      <c r="B20" s="28"/>
+      <c r="C20" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="5"/>
       <c r="F20" s="1">
         <f>E20*0.1</f>
@@ -2272,14 +2289,14 @@
       </c>
     </row>
     <row r="21" spans="1:23">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="25" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="5"/>
       <c r="F21" s="1">
         <f>E21*0.1</f>
@@ -2322,14 +2339,14 @@
       </c>
     </row>
     <row r="22" spans="1:23">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="5"/>
       <c r="F22" s="1">
         <f>E22*0.1</f>
@@ -2372,14 +2389,14 @@
       </c>
     </row>
     <row r="23" spans="1:23">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="25" t="s">
+      <c r="B23" s="28"/>
+      <c r="C23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="26"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="5"/>
       <c r="F23" s="1">
         <f>E23*0.1</f>
@@ -2422,14 +2439,14 @@
       </c>
     </row>
     <row r="24" spans="1:23">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="26"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="5"/>
       <c r="F24" s="1">
         <f>E24*0.1</f>
@@ -2472,14 +2489,14 @@
       </c>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="25" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="26"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="5"/>
       <c r="F25" s="1">
         <f>E25*0.1</f>
@@ -2522,14 +2539,14 @@
       </c>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="25" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="26"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="5"/>
       <c r="F26" s="1">
         <f>E26*0.1</f>
@@ -2572,14 +2589,14 @@
       </c>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="26"/>
+      <c r="D27" s="28"/>
       <c r="E27" s="5"/>
       <c r="F27" s="1">
         <f>E27*0.1</f>
@@ -2622,14 +2639,14 @@
       </c>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="26"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="5"/>
       <c r="F28" s="1">
         <f>E28*0.1</f>
@@ -2672,14 +2689,14 @@
       </c>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="25" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="26"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="5"/>
       <c r="F29" s="1">
         <f>E29*0.1</f>
@@ -2722,14 +2739,14 @@
       </c>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="5"/>
       <c r="F30" s="1">
         <f>E30*0.1</f>
@@ -2772,14 +2789,14 @@
       </c>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="5"/>
       <c r="F31" s="1">
         <f>E31*0.1</f>
@@ -2822,14 +2839,14 @@
       </c>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="26"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="5"/>
       <c r="F32" s="1">
         <f>E32*0.1</f>
@@ -2872,14 +2889,14 @@
       </c>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="31"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="5"/>
       <c r="F33" s="1">
         <f>E33*0.1</f>
@@ -2922,14 +2939,14 @@
       </c>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25" t="s">
+      <c r="B34" s="28"/>
+      <c r="C34" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="26"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="5"/>
       <c r="F34" s="1">
         <f>E34*0.1</f>
@@ -2972,14 +2989,14 @@
       </c>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="25" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="26"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="5"/>
       <c r="F35" s="1">
         <f>E35*0.1</f>
@@ -3022,14 +3039,14 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="26"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="5"/>
       <c r="F36" s="1">
         <f>E36*0.1</f>
@@ -3072,14 +3089,14 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="25" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="26"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="5"/>
       <c r="F37" s="1">
         <f>E37*0.1</f>
@@ -3122,14 +3139,14 @@
       </c>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="25" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="26"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="5"/>
       <c r="F38" s="1">
         <f>E38*0.1</f>
@@ -3172,14 +3189,14 @@
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="25" t="s">
+      <c r="B39" s="28"/>
+      <c r="C39" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="26"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="5"/>
       <c r="F39" s="1">
         <f>E39*0.1</f>
@@ -3222,14 +3239,14 @@
       </c>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="25" t="s">
+      <c r="B40" s="28"/>
+      <c r="C40" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="26"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="13"/>
       <c r="F40" s="1">
         <f>E40*0.1</f>
@@ -3272,14 +3289,14 @@
       </c>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="33"/>
+      <c r="C41" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="31"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="5"/>
       <c r="F41" s="1">
         <f>E41*0.1</f>
@@ -3322,14 +3339,14 @@
       </c>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="26"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="5"/>
       <c r="F42" s="1">
         <f>E42*0.1</f>
@@ -3372,14 +3389,14 @@
       </c>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="25" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="26"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="5"/>
       <c r="F43" s="1">
         <f>E43*0.1</f>
@@ -3422,14 +3439,14 @@
       </c>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="25" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="26"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="5"/>
       <c r="F44" s="1">
         <f>E44*0.1</f>
@@ -3472,14 +3489,14 @@
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="25" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="26"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="5"/>
       <c r="F45" s="1">
         <f>E45*0.1</f>
@@ -3522,14 +3539,14 @@
       </c>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="25" t="s">
+      <c r="B46" s="28"/>
+      <c r="C46" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="26"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="5"/>
       <c r="F46" s="1">
         <f>E46*0.1</f>
@@ -3572,14 +3589,14 @@
       </c>
     </row>
     <row r="47" spans="1:23">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="25" t="s">
+      <c r="B47" s="28"/>
+      <c r="C47" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="26"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="5"/>
       <c r="F47" s="1">
         <f>E47*0.1</f>
@@ -3622,14 +3639,14 @@
       </c>
     </row>
     <row r="48" spans="1:23">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30" t="s">
+      <c r="B48" s="33"/>
+      <c r="C48" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="31"/>
+      <c r="D48" s="33"/>
       <c r="E48" s="5"/>
       <c r="F48" s="1">
         <f>E48*0.1</f>
@@ -3672,14 +3689,14 @@
       </c>
     </row>
     <row r="49" spans="1:23">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30" t="s">
+      <c r="B49" s="33"/>
+      <c r="C49" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="31"/>
+      <c r="D49" s="33"/>
       <c r="E49" s="5"/>
       <c r="F49" s="1">
         <f>E49*0.1</f>
@@ -3722,14 +3739,14 @@
       </c>
     </row>
     <row r="50" spans="1:23">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30" t="s">
+      <c r="B50" s="33"/>
+      <c r="C50" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="31"/>
+      <c r="D50" s="33"/>
       <c r="E50" s="5"/>
       <c r="F50" s="1">
         <f>E50*0.1</f>
@@ -3772,14 +3789,14 @@
       </c>
     </row>
     <row r="51" spans="1:23">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30" t="s">
+      <c r="B51" s="33"/>
+      <c r="C51" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="31"/>
+      <c r="D51" s="33"/>
       <c r="E51" s="5"/>
       <c r="F51" s="1">
         <f>E51*0.1</f>
@@ -3822,14 +3839,14 @@
       </c>
     </row>
     <row r="52" spans="1:23">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="33"/>
+      <c r="C52" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="33"/>
       <c r="E52" s="5"/>
       <c r="F52" s="1">
         <f>E52*0.1</f>
@@ -4049,84 +4066,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26"/>
       <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.1</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="3">
         <v>0.4</v>
       </c>
@@ -4147,14 +4164,14 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -4176,14 +4193,14 @@
       <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="13">
         <v>4.8</v>
       </c>
@@ -4225,14 +4242,14 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="25" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="5">
         <v>4.0999999999999996</v>
       </c>
@@ -4274,14 +4291,14 @@
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="5">
         <v>2.5</v>
       </c>
@@ -4323,14 +4340,14 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="5">
         <v>4.8</v>
       </c>
@@ -4372,14 +4389,14 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="5">
         <v>5</v>
       </c>
@@ -4421,14 +4438,14 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="25" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="5">
         <v>4.7</v>
       </c>
@@ -4470,14 +4487,14 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="5">
         <v>4.8</v>
       </c>
@@ -4519,14 +4536,14 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -4568,14 +4585,14 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="33"/>
+      <c r="C16" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="33"/>
       <c r="E16" s="5">
         <v>4.8</v>
       </c>
@@ -4617,14 +4634,14 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="26"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -4666,14 +4683,14 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="25" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -4715,14 +4732,14 @@
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="25" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="5">
         <v>4</v>
       </c>
@@ -4764,14 +4781,14 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="25" t="s">
+      <c r="B20" s="28"/>
+      <c r="C20" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="5">
         <v>4.8</v>
       </c>
@@ -4813,14 +4830,14 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="25" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="5">
         <v>3.6</v>
       </c>
@@ -4862,14 +4879,14 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="5">
         <v>4</v>
       </c>
@@ -4911,14 +4928,14 @@
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="25" t="s">
+      <c r="B23" s="28"/>
+      <c r="C23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="26"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="5">
         <v>4.4000000000000004</v>
       </c>
@@ -4960,14 +4977,14 @@
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="26"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="5">
         <v>5</v>
       </c>
@@ -5009,14 +5026,14 @@
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="25" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="26"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="5">
         <v>4.7</v>
       </c>
@@ -5058,14 +5075,14 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="25" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="26"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="5">
         <v>5</v>
       </c>
@@ -5107,14 +5124,14 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="26"/>
+      <c r="D27" s="28"/>
       <c r="E27" s="5">
         <v>5</v>
       </c>
@@ -5156,14 +5173,14 @@
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="26"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -5205,14 +5222,14 @@
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="25" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="26"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="5">
         <v>4.0999999999999996</v>
       </c>
@@ -5254,14 +5271,14 @@
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="5">
         <v>4.3</v>
       </c>
@@ -5303,14 +5320,14 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -5352,14 +5369,14 @@
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="26"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="5">
         <v>4.3</v>
       </c>
@@ -5401,14 +5418,14 @@
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="31"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="5">
         <v>4</v>
       </c>
@@ -5450,14 +5467,14 @@
       </c>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25" t="s">
+      <c r="B34" s="28"/>
+      <c r="C34" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="26"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -5499,14 +5516,14 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="25" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="26"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="5">
         <v>3.1</v>
       </c>
@@ -5548,14 +5565,14 @@
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="26"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="5">
         <v>4.9000000000000004</v>
       </c>
@@ -5597,14 +5614,14 @@
       </c>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="25" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="26"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="5">
         <v>5</v>
       </c>
@@ -5646,14 +5663,14 @@
       </c>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="25" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="26"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="5">
         <v>4.0999999999999996</v>
       </c>
@@ -5695,14 +5712,14 @@
       </c>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="25" t="s">
+      <c r="B39" s="28"/>
+      <c r="C39" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="26"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="5">
         <v>5</v>
       </c>
@@ -5744,14 +5761,14 @@
       </c>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="25" t="s">
+      <c r="B40" s="28"/>
+      <c r="C40" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="26"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="13">
         <v>4.9000000000000004</v>
       </c>
@@ -5793,14 +5810,14 @@
       </c>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="33"/>
+      <c r="C41" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="31"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="5">
         <v>4.9000000000000004</v>
       </c>
@@ -5842,14 +5859,14 @@
       </c>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="26"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="5">
         <v>4.8</v>
       </c>
@@ -5891,14 +5908,14 @@
       </c>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="25" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="26"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="5">
         <v>3.6</v>
       </c>
@@ -5940,14 +5957,14 @@
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="25" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="26"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="5">
         <v>4.9000000000000004</v>
       </c>
@@ -5989,14 +6006,14 @@
       </c>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="25" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="26"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="5">
         <v>4.7</v>
       </c>
@@ -6038,14 +6055,14 @@
       </c>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="25" t="s">
+      <c r="B46" s="28"/>
+      <c r="C46" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="26"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="5">
         <v>2.5</v>
       </c>
@@ -6087,14 +6104,14 @@
       </c>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="25" t="s">
+      <c r="B47" s="28"/>
+      <c r="C47" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="26"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="5">
         <v>4.4000000000000004</v>
       </c>
@@ -6136,14 +6153,14 @@
       </c>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30" t="s">
+      <c r="B48" s="33"/>
+      <c r="C48" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="31"/>
+      <c r="D48" s="33"/>
       <c r="E48" s="5">
         <v>3.5</v>
       </c>
@@ -6185,14 +6202,14 @@
       </c>
     </row>
     <row r="49" spans="1:15">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30" t="s">
+      <c r="B49" s="33"/>
+      <c r="C49" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="31"/>
+      <c r="D49" s="33"/>
       <c r="E49" s="5">
         <v>4</v>
       </c>
@@ -6234,14 +6251,14 @@
       </c>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30" t="s">
+      <c r="B50" s="33"/>
+      <c r="C50" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="31"/>
+      <c r="D50" s="33"/>
       <c r="E50" s="5">
         <v>4.7</v>
       </c>
@@ -6283,14 +6300,14 @@
       </c>
     </row>
     <row r="51" spans="1:15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30" t="s">
+      <c r="B51" s="33"/>
+      <c r="C51" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="31"/>
+      <c r="D51" s="33"/>
       <c r="E51" s="5">
         <v>4.0999999999999996</v>
       </c>
@@ -6332,14 +6349,14 @@
       </c>
     </row>
     <row r="52" spans="1:15">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="33"/>
+      <c r="C52" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="33"/>
       <c r="E52" s="5">
         <v>3.1</v>
       </c>
@@ -6549,88 +6566,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
       <c r="J1" s="16"/>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="39" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
       <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
       <c r="J3" s="16"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
       <c r="J4" s="16"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="32" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="4">
         <v>0.1</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="15"/>
       <c r="K6" s="3">
         <v>0.4</v>
@@ -6641,10 +6658,10 @@
       <c r="M6" s="4">
         <v>0.5</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="37"/>
+      <c r="O6" s="39"/>
       <c r="P6" s="4" t="s">
         <v>13</v>
       </c>
@@ -6662,14 +6679,14 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="8" t="s">
         <v>118</v>
       </c>
@@ -6702,14 +6719,14 @@
       <c r="T7" s="8"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="13">
         <v>5</v>
       </c>
@@ -6769,14 +6786,14 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="25" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="5">
         <v>5</v>
       </c>
@@ -6836,14 +6853,14 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="5">
         <v>5</v>
       </c>
@@ -6903,14 +6920,14 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="5">
         <v>5</v>
       </c>
@@ -6970,14 +6987,14 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="5">
         <v>5</v>
       </c>
@@ -7037,14 +7054,14 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="25" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="5">
         <v>5</v>
       </c>
@@ -7104,14 +7121,14 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="5">
         <v>3.9</v>
       </c>
@@ -7171,14 +7188,14 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="5">
         <v>5</v>
       </c>
@@ -7238,14 +7255,14 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="33"/>
+      <c r="C16" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="33"/>
       <c r="E16" s="5">
         <v>5</v>
       </c>
@@ -7303,14 +7320,14 @@
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="26"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="5">
         <v>5</v>
       </c>
@@ -7370,14 +7387,14 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="25" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="5">
         <v>5</v>
       </c>
@@ -7437,14 +7454,14 @@
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="25" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="5">
         <v>5</v>
       </c>
@@ -7502,14 +7519,14 @@
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="25" t="s">
+      <c r="B20" s="28"/>
+      <c r="C20" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="5">
         <v>3.9</v>
       </c>
@@ -7569,14 +7586,14 @@
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="25" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="5">
         <v>5</v>
       </c>
@@ -7636,14 +7653,14 @@
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="5">
         <v>5</v>
       </c>
@@ -7701,14 +7718,14 @@
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="25" t="s">
+      <c r="B23" s="28"/>
+      <c r="C23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="26"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="5">
         <v>5</v>
       </c>
@@ -7768,14 +7785,14 @@
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="26"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="5">
         <v>5</v>
       </c>
@@ -7833,14 +7850,14 @@
       </c>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="25" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="26"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="5">
         <v>5</v>
       </c>
@@ -7898,14 +7915,14 @@
       </c>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="25" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="26"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="5">
         <v>5</v>
       </c>
@@ -7965,14 +7982,14 @@
       </c>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="26"/>
+      <c r="D27" s="28"/>
       <c r="E27" s="5">
         <v>5</v>
       </c>
@@ -8032,14 +8049,14 @@
       </c>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="26"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="5">
         <v>5</v>
       </c>
@@ -8099,14 +8116,14 @@
       </c>
     </row>
     <row r="29" spans="1:20">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="25" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="26"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="5">
         <v>3.9</v>
       </c>
@@ -8166,14 +8183,14 @@
       </c>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="5">
         <v>3.9</v>
       </c>
@@ -8233,14 +8250,14 @@
       </c>
     </row>
     <row r="31" spans="1:20">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="5">
         <v>5</v>
       </c>
@@ -8300,14 +8317,14 @@
       </c>
     </row>
     <row r="32" spans="1:20">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="26"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="5">
         <v>3.9</v>
       </c>
@@ -8367,14 +8384,14 @@
       </c>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="31"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="5">
         <v>5</v>
       </c>
@@ -8434,14 +8451,14 @@
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25" t="s">
+      <c r="B34" s="28"/>
+      <c r="C34" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="26"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="5">
         <v>5</v>
       </c>
@@ -8501,14 +8518,14 @@
       </c>
     </row>
     <row r="35" spans="1:20">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="25" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="26"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="5">
         <v>5</v>
       </c>
@@ -8568,14 +8585,14 @@
       </c>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="26"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="5">
         <v>5</v>
       </c>
@@ -8635,14 +8652,14 @@
       </c>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="25" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="26"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="5">
         <v>5</v>
       </c>
@@ -8702,14 +8719,14 @@
       </c>
     </row>
     <row r="38" spans="1:20">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="25" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="26"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="5">
         <v>3.9</v>
       </c>
@@ -8769,14 +8786,14 @@
       </c>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="25" t="s">
+      <c r="B39" s="28"/>
+      <c r="C39" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="26"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="5">
         <v>5</v>
       </c>
@@ -8834,14 +8851,14 @@
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="25" t="s">
+      <c r="B40" s="28"/>
+      <c r="C40" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="26"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="13">
         <v>5</v>
       </c>
@@ -8901,14 +8918,14 @@
       </c>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="33"/>
+      <c r="C41" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="31"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="5">
         <v>5</v>
       </c>
@@ -8968,14 +8985,14 @@
       </c>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="26"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="5">
         <v>5</v>
       </c>
@@ -9035,14 +9052,14 @@
       </c>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="25" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="26"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="5">
         <v>3.9</v>
       </c>
@@ -9100,14 +9117,14 @@
       </c>
     </row>
     <row r="44" spans="1:20">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="25" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="26"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="5">
         <v>5</v>
       </c>
@@ -9167,14 +9184,14 @@
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="25" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="26"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="5">
         <v>3.9</v>
       </c>
@@ -9234,14 +9251,14 @@
       </c>
     </row>
     <row r="46" spans="1:20">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="25" t="s">
+      <c r="B46" s="28"/>
+      <c r="C46" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="26"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="5">
         <v>5</v>
       </c>
@@ -9299,14 +9316,14 @@
       </c>
     </row>
     <row r="47" spans="1:20">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="25" t="s">
+      <c r="B47" s="28"/>
+      <c r="C47" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="26"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="5">
         <v>5</v>
       </c>
@@ -9366,14 +9383,14 @@
       </c>
     </row>
     <row r="48" spans="1:20">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30" t="s">
+      <c r="B48" s="33"/>
+      <c r="C48" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="31"/>
+      <c r="D48" s="33"/>
       <c r="E48" s="5">
         <v>3.9</v>
       </c>
@@ -9433,14 +9450,14 @@
       </c>
     </row>
     <row r="49" spans="1:20">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30" t="s">
+      <c r="B49" s="33"/>
+      <c r="C49" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="31"/>
+      <c r="D49" s="33"/>
       <c r="E49" s="5">
         <v>5</v>
       </c>
@@ -9498,14 +9515,14 @@
       </c>
     </row>
     <row r="50" spans="1:20">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30" t="s">
+      <c r="B50" s="33"/>
+      <c r="C50" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="31"/>
+      <c r="D50" s="33"/>
       <c r="E50" s="5">
         <v>3.9</v>
       </c>
@@ -9565,14 +9582,14 @@
       </c>
     </row>
     <row r="51" spans="1:20">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30" t="s">
+      <c r="B51" s="33"/>
+      <c r="C51" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="31"/>
+      <c r="D51" s="33"/>
       <c r="E51" s="5">
         <v>5</v>
       </c>
@@ -9632,14 +9649,14 @@
       </c>
     </row>
     <row r="52" spans="1:20">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="33"/>
+      <c r="C52" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="33"/>
       <c r="E52" s="5">
         <v>5</v>
       </c>
@@ -9865,90 +9882,91 @@
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" customWidth="1"/>
     <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.05</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="3">
         <v>0.5</v>
       </c>
@@ -9958,7 +9976,7 @@
       <c r="L6" s="4">
         <v>0.45</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="18" t="s">
         <v>12</v>
       </c>
       <c r="N6" s="11" t="s">
@@ -9975,14 +9993,14 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -9999,7 +10017,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="8"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="19" t="s">
         <v>123</v>
       </c>
       <c r="N7" s="10"/>
@@ -10008,14 +10026,14 @@
       <c r="Q7" s="8"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="13">
         <v>4.0999999999999996</v>
       </c>
@@ -10023,17 +10041,25 @@
         <f>E8*0.05</f>
         <v>0.20499999999999999</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="5" t="e">
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J8" s="5">
         <f>AVERAGE(G8:I8)*0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K8" s="1">
+        <v>4</v>
+      </c>
       <c r="L8" s="6">
         <f>K8*0.45</f>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="6">
         <v>4</v>
@@ -10042,28 +10068,28 @@
         <f>(SUM(M8:M8)/5)*0.3</f>
         <v>0.24</v>
       </c>
-      <c r="O8" s="6" t="e">
+      <c r="O8" s="6">
         <f>L8+J8+F8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="6" t="e">
+        <v>4.3383333333333338</v>
+      </c>
+      <c r="P8" s="6">
         <f>INT(O8*10)/10+IF(MOD(O8*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q8" s="1" t="e">
+        <v>4.3</v>
+      </c>
+      <c r="Q8" s="1" t="str">
         <f>IF(O8&lt;3,3-O8,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="25" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="5">
         <v>3.7</v>
       </c>
@@ -10071,17 +10097,25 @@
         <f t="shared" ref="F9:F52" si="0">E9*0.05</f>
         <v>0.18500000000000003</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="5" t="e">
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J9" s="5">
         <f t="shared" ref="J9:J52" si="1">AVERAGE(G9:I9)*0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3.9</v>
+      </c>
       <c r="L9" s="6">
         <f t="shared" ref="L9:L52" si="2">K9*0.45</f>
-        <v>0</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="M9" s="6">
         <v>1</v>
@@ -10090,28 +10124,28 @@
         <f>(SUM(M9:M9)/5)*0.5</f>
         <v>0.1</v>
       </c>
-      <c r="O9" s="6" t="e">
+      <c r="O9" s="6">
         <f>L9+J9+F9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="6" t="e">
+        <v>4.1899999999999995</v>
+      </c>
+      <c r="P9" s="6">
         <f>INT(O9*10)/10+IF(MOD(O9*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q9" s="1" t="e">
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="Q9" s="1" t="str">
         <f>IF(O9&lt;3,3-O9,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="5">
         <v>3.3</v>
       </c>
@@ -10119,45 +10153,53 @@
         <f t="shared" si="0"/>
         <v>0.16500000000000001</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="5" t="e">
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>2.3666666666666667</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.5</v>
+      </c>
       <c r="L10" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="6">
         <f>(SUM(M10:M10)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O10" s="6" t="e">
+      <c r="O10" s="6">
         <f>L10+J10+F10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P10" s="6" t="e">
+        <v>4.1066666666666665</v>
+      </c>
+      <c r="P10" s="6">
         <f>INT(O10*10)/10+IF(MOD(O10*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q10" s="1" t="e">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q10" s="1" t="str">
         <f>IF(O10&lt;3,3-O10,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="5">
         <v>4.0999999999999996</v>
       </c>
@@ -10165,17 +10207,25 @@
         <f t="shared" si="0"/>
         <v>0.20499999999999999</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="5" t="e">
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K11" s="1">
+        <v>4</v>
+      </c>
       <c r="L11" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" s="6">
         <v>5</v>
@@ -10184,28 +10234,28 @@
         <f>(SUM(M11:M11)/5)*0.5</f>
         <v>0.5</v>
       </c>
-      <c r="O11" s="6" t="e">
+      <c r="O11" s="6">
         <f>L11+J11+F11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="6" t="e">
+        <v>4.3383333333333338</v>
+      </c>
+      <c r="P11" s="6">
         <f>INT(O11*10)/10+IF(MOD(O11*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q11" s="1" t="e">
+        <v>4.3</v>
+      </c>
+      <c r="Q11" s="1" t="str">
         <f>IF(O11&lt;3,3-O11,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="5">
         <v>4.3</v>
       </c>
@@ -10213,17 +10263,25 @@
         <f t="shared" si="0"/>
         <v>0.215</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="5" t="e">
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K12" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K12" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L12" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M12" s="6">
         <v>10.1</v>
@@ -10232,28 +10290,28 @@
         <f>(SUM(M12:M12)/5)*0.5</f>
         <v>1.01</v>
       </c>
-      <c r="O12" s="6" t="e">
+      <c r="O12" s="6">
         <f>L12+J12+F12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="6" t="e">
+        <v>4.836666666666666</v>
+      </c>
+      <c r="P12" s="6">
         <f>INT(O12*10)/10+IF(MOD(O12*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q12" s="1" t="e">
+        <v>4.8</v>
+      </c>
+      <c r="Q12" s="1" t="str">
         <f>IF(O12&lt;3,3-O12,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="25" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="5">
         <v>4.8</v>
       </c>
@@ -10261,45 +10319,53 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="5" t="e">
+      <c r="G13" s="1">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K13" s="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5</v>
+      </c>
       <c r="L13" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6">
         <f>(SUM(M13:M13)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O13" s="6" t="e">
+      <c r="O13" s="6">
         <f>L13+J13+F13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" s="6" t="e">
+        <v>4.8233333333333341</v>
+      </c>
+      <c r="P13" s="6">
         <f>INT(O13*10)/10+IF(MOD(O13*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q13" s="1" t="e">
+        <v>4.8</v>
+      </c>
+      <c r="Q13" s="1" t="str">
         <f>IF(O13&lt;3,3-O13,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="5">
         <v>4.25</v>
       </c>
@@ -10307,17 +10373,25 @@
         <f t="shared" si="0"/>
         <v>0.21250000000000002</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="5" t="e">
+      <c r="G14" s="1">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I14" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>2.35</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
       <c r="L14" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M14" s="6">
         <v>8</v>
@@ -10326,28 +10400,28 @@
         <f>(SUM(M14:M14)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O14" s="6" t="e">
+      <c r="O14" s="6">
         <f>L14+J14+F14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P14" s="6" t="e">
+        <v>3.0125000000000002</v>
+      </c>
+      <c r="P14" s="6">
         <f>INT(O14*10)/10+IF(MOD(O14*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q14" s="1" t="e">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="1" t="str">
         <f>IF(O14&lt;3,3-O14,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="5">
         <v>5</v>
       </c>
@@ -10355,89 +10429,107 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="5" t="e">
+      <c r="G15" s="1">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="K15" s="1">
+        <v>5</v>
+      </c>
       <c r="L15" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6">
         <f>(SUM(M15:M15)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O15" s="6" t="e">
+      <c r="O15" s="6">
         <f>L15+J15+F15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="6" t="e">
+        <v>4.75</v>
+      </c>
+      <c r="P15" s="6">
         <f>INT(O15*10)/10+IF(MOD(O15*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q15" s="1" t="e">
+        <v>4.8</v>
+      </c>
+      <c r="Q15" s="1" t="str">
         <f>IF(O15&lt;3,3-O15,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="33"/>
+      <c r="C16" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="5"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
       <c r="F16" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="5" t="e">
+      <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="1"/>
+        <v>2.3666666666666667</v>
+      </c>
+      <c r="K16" s="1">
+        <v>5</v>
+      </c>
       <c r="L16" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M16" s="6"/>
       <c r="N16" s="6">
         <f>(SUM(M16:M16)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O16" s="6" t="e">
+      <c r="O16" s="6">
         <f>L16+J16+F16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P16" s="6" t="e">
+        <v>4.6166666666666671</v>
+      </c>
+      <c r="P16" s="6">
         <f>INT(O16*10)/10+IF(MOD(O16*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q16" s="1" t="e">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q16" s="1" t="str">
         <f>IF(O16&lt;3,3-O16,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="26"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="5">
         <v>4.8</v>
       </c>
@@ -10445,17 +10537,25 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="5" t="e">
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K17" s="1"/>
+        <v>2.4666666666666668</v>
+      </c>
+      <c r="K17" s="1">
+        <v>4.5</v>
+      </c>
       <c r="L17" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="M17" s="6">
         <v>8.5</v>
@@ -10464,28 +10564,28 @@
         <f>(SUM(M17:M17)/5)*0.5</f>
         <v>0.85</v>
       </c>
-      <c r="O17" s="6" t="e">
+      <c r="O17" s="6">
         <f>L17+J17+F17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P17" s="6" t="e">
+        <v>4.7316666666666674</v>
+      </c>
+      <c r="P17" s="6">
         <f>INT(O17*10)/10+IF(MOD(O17*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q17" s="1" t="e">
+        <v>4.7</v>
+      </c>
+      <c r="Q17" s="1" t="str">
         <f>IF(O17&lt;3,3-O17,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="25" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="5">
         <v>5</v>
       </c>
@@ -10493,17 +10593,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="5" t="e">
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K18" s="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="K18" s="1">
+        <v>5</v>
+      </c>
       <c r="L18" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M18" s="6">
         <v>4</v>
@@ -10512,28 +10620,28 @@
         <f>(SUM(M18:M18)/5)*0.5</f>
         <v>0.4</v>
       </c>
-      <c r="O18" s="6" t="e">
+      <c r="O18" s="6">
         <f>L18+J18+F18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P18" s="6" t="e">
+        <v>4.75</v>
+      </c>
+      <c r="P18" s="6">
         <f>INT(O18*10)/10+IF(MOD(O18*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q18" s="1" t="e">
+        <v>4.8</v>
+      </c>
+      <c r="Q18" s="1" t="str">
         <f>IF(O18&lt;3,3-O18,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="25" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="5">
         <v>4.8</v>
       </c>
@@ -10541,17 +10649,25 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="5" t="e">
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K19" s="1"/>
+        <v>2.4666666666666668</v>
+      </c>
+      <c r="K19" s="1">
+        <v>5</v>
+      </c>
       <c r="L19" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M19" s="6">
         <v>8</v>
@@ -10560,28 +10676,28 @@
         <f>(SUM(M19:M19)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O19" s="6" t="e">
+      <c r="O19" s="6">
         <f>L19+J19+F19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P19" s="6" t="e">
+        <v>4.956666666666667</v>
+      </c>
+      <c r="P19" s="6">
         <f>INT(O19*10)/10+IF(MOD(O19*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q19" s="1" t="e">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="1" t="str">
         <f>IF(O19&lt;3,3-O19,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="25" t="s">
+      <c r="B20" s="28"/>
+      <c r="C20" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="5">
         <v>4.25</v>
       </c>
@@ -10589,45 +10705,53 @@
         <f t="shared" si="0"/>
         <v>0.21250000000000002</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="5" t="e">
+      <c r="G20" s="1">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I20" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K20" s="1"/>
+        <v>2.35</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
       <c r="L20" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M20" s="6"/>
       <c r="N20" s="6">
         <f>(SUM(M20:M20)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O20" s="6" t="e">
+      <c r="O20" s="6">
         <f>L20+J20+F20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P20" s="6" t="e">
+        <v>3.0125000000000002</v>
+      </c>
+      <c r="P20" s="6">
         <f>INT(O20*10)/10+IF(MOD(O20*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q20" s="1" t="e">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1" t="str">
         <f>IF(O20&lt;3,3-O20,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="25" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="5">
         <v>4.5</v>
       </c>
@@ -10635,45 +10759,53 @@
         <f t="shared" si="0"/>
         <v>0.22500000000000001</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="5" t="e">
+      <c r="G21" s="1">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="1"/>
+        <v>1.4666666666666668</v>
+      </c>
+      <c r="K21" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L21" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9350000000000001</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6">
         <f>(SUM(M21:M21)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O21" s="6" t="e">
+      <c r="O21" s="6">
         <f>L21+J21+F21</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="6" t="e">
+        <v>3.6266666666666669</v>
+      </c>
+      <c r="P21" s="6">
         <f>INT(O21*10)/10+IF(MOD(O21*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q21" s="1" t="e">
+        <v>3.6</v>
+      </c>
+      <c r="Q21" s="1" t="str">
         <f>IF(O21&lt;3,3-O21,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="5">
         <v>4.8</v>
       </c>
@@ -10681,17 +10813,25 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="5" t="e">
+      <c r="G22" s="1">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K22" s="1"/>
+        <v>2.4666666666666668</v>
+      </c>
+      <c r="K22" s="1">
+        <v>5</v>
+      </c>
       <c r="L22" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M22" s="6">
         <v>8</v>
@@ -10700,28 +10840,28 @@
         <f>(SUM(M22:M22)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O22" s="6" t="e">
+      <c r="O22" s="6">
         <f>L22+J22+F22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P22" s="6" t="e">
+        <v>4.956666666666667</v>
+      </c>
+      <c r="P22" s="6">
         <f>INT(O22*10)/10+IF(MOD(O22*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q22" s="1" t="e">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="1" t="str">
         <f>IF(O22&lt;3,3-O22,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="25" t="s">
+      <c r="B23" s="28"/>
+      <c r="C23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="26"/>
+      <c r="D23" s="28"/>
       <c r="E23" s="5">
         <v>4.4000000000000004</v>
       </c>
@@ -10729,61 +10869,79 @@
         <f t="shared" si="0"/>
         <v>0.22000000000000003</v>
       </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="5" t="e">
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I23" s="1">
+        <v>5</v>
+      </c>
+      <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K23" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4</v>
+      </c>
       <c r="L23" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6">
         <f>(SUM(M23:M23)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O23" s="6" t="e">
+      <c r="O23" s="6">
         <f>L23+J23+F23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P23" s="6" t="e">
+        <v>4.503333333333333</v>
+      </c>
+      <c r="P23" s="6">
         <f>INT(O23*10)/10+IF(MOD(O23*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q23" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q23" s="1" t="str">
         <f>IF(O23&lt;3,3-O23,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="5"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="5">
+        <v>5</v>
+      </c>
       <c r="F24" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="5" t="e">
+        <v>0.25</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K24" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K24" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L24" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M24" s="6">
         <v>9</v>
@@ -10792,28 +10950,28 @@
         <f>(SUM(M24:M24)/5)*0.5</f>
         <v>0.9</v>
       </c>
-      <c r="O24" s="6" t="e">
+      <c r="O24" s="6">
         <f>L24+J24+F24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P24" s="6" t="e">
+        <v>4.8716666666666661</v>
+      </c>
+      <c r="P24" s="6">
         <f>INT(O24*10)/10+IF(MOD(O24*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q24" s="1" t="e">
+        <v>4.8999999999999995</v>
+      </c>
+      <c r="Q24" s="1" t="str">
         <f>IF(O24&lt;3,3-O24,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="25" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="26"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="5">
         <v>4.8</v>
       </c>
@@ -10821,17 +10979,25 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="5" t="e">
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K25" s="1"/>
+        <v>2.3666666666666667</v>
+      </c>
+      <c r="K25" s="1">
+        <v>5</v>
+      </c>
       <c r="L25" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M25" s="6">
         <v>5</v>
@@ -10840,28 +11006,28 @@
         <f>(SUM(M25:M25)/5)*0.5</f>
         <v>0.5</v>
       </c>
-      <c r="O25" s="6" t="e">
+      <c r="O25" s="6">
         <f>L25+J25+F25</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P25" s="6" t="e">
+        <v>4.8566666666666674</v>
+      </c>
+      <c r="P25" s="6">
         <f>INT(O25*10)/10+IF(MOD(O25*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q25" s="1" t="e">
+        <v>4.8999999999999995</v>
+      </c>
+      <c r="Q25" s="1" t="str">
         <f>IF(O25&lt;3,3-O25,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="25" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="26"/>
+      <c r="D26" s="28"/>
       <c r="E26" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -10869,17 +11035,25 @@
         <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="5" t="e">
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I26" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>4.7</v>
+      </c>
       <c r="L26" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.1150000000000002</v>
       </c>
       <c r="M26" s="6">
         <v>9</v>
@@ -10888,28 +11062,28 @@
         <f>(SUM(M26:M26)/5)*0.5</f>
         <v>0.9</v>
       </c>
-      <c r="O26" s="6" t="e">
+      <c r="O26" s="6">
         <f>L26+J26+F26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P26" s="6" t="e">
+        <v>4.745000000000001</v>
+      </c>
+      <c r="P26" s="6">
         <f>INT(O26*10)/10+IF(MOD(O26*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q26" s="1" t="e">
+        <v>4.7</v>
+      </c>
+      <c r="Q26" s="1" t="str">
         <f>IF(O26&lt;3,3-O26,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="26"/>
+      <c r="D27" s="28"/>
       <c r="E27" s="5">
         <v>5</v>
       </c>
@@ -10917,17 +11091,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="5" t="e">
+      <c r="G27" s="1">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="1"/>
+        <v>2.4499999999999997</v>
+      </c>
+      <c r="K27" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L27" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M27" s="6">
         <v>11</v>
@@ -10936,28 +11118,28 @@
         <f>(SUM(M27:M27)/5)*0.5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="O27" s="6" t="e">
+      <c r="O27" s="6">
         <f>L27+J27+F27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P27" s="6" t="e">
+        <v>4.9049999999999994</v>
+      </c>
+      <c r="P27" s="6">
         <f>INT(O27*10)/10+IF(MOD(O27*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q27" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q27" s="1" t="str">
         <f>IF(O27&lt;3,3-O27,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="26"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="5">
         <v>4.8</v>
       </c>
@@ -10965,17 +11147,25 @@
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="5" t="e">
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="1"/>
+        <v>2.4666666666666668</v>
+      </c>
+      <c r="K28" s="1">
+        <v>4.5</v>
+      </c>
       <c r="L28" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="M28" s="6">
         <v>8</v>
@@ -10984,28 +11174,28 @@
         <f>(SUM(M28:M28)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O28" s="6" t="e">
+      <c r="O28" s="6">
         <f>L28+J28+F28</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P28" s="6" t="e">
+        <v>4.7316666666666674</v>
+      </c>
+      <c r="P28" s="6">
         <f>INT(O28*10)/10+IF(MOD(O28*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q28" s="1" t="e">
+        <v>4.7</v>
+      </c>
+      <c r="Q28" s="1" t="str">
         <f>IF(O28&lt;3,3-O28,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="25" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="26"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="5">
         <v>4.3</v>
       </c>
@@ -11013,17 +11203,25 @@
         <f t="shared" si="0"/>
         <v>0.215</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="5" t="e">
+      <c r="G29" s="1">
+        <v>5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5</v>
+      </c>
+      <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K29" s="1">
+        <v>5</v>
+      </c>
       <c r="L29" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M29" s="6">
         <v>11</v>
@@ -11032,28 +11230,28 @@
         <f>(SUM(M29:M29)/5)*0.5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="O29" s="6" t="e">
+      <c r="O29" s="6">
         <f>L29+J29+F29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P29" s="6" t="e">
+        <v>4.9483333333333333</v>
+      </c>
+      <c r="P29" s="6">
         <f>INT(O29*10)/10+IF(MOD(O29*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q29" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q29" s="1" t="str">
         <f>IF(O29&lt;3,3-O29,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="5">
         <v>4.5</v>
       </c>
@@ -11061,17 +11259,25 @@
         <f t="shared" si="0"/>
         <v>0.22500000000000001</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="5" t="e">
+      <c r="G30" s="1">
+        <v>5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I30" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="1"/>
+        <v>2.35</v>
+      </c>
+      <c r="K30" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L30" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9350000000000001</v>
       </c>
       <c r="M30" s="6">
         <v>8</v>
@@ -11080,28 +11286,28 @@
         <f>(SUM(M30:M30)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O30" s="6" t="e">
+      <c r="O30" s="6">
         <f>L30+J30+F30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P30" s="6" t="e">
+        <v>4.51</v>
+      </c>
+      <c r="P30" s="6">
         <f>INT(O30*10)/10+IF(MOD(O30*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q30" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q30" s="1" t="str">
         <f>IF(O30&lt;3,3-O30,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="5">
         <v>5</v>
       </c>
@@ -11109,17 +11315,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="5" t="e">
+      <c r="G31" s="1">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I31" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K31" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="L31" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="M31" s="6">
         <v>5</v>
@@ -11128,28 +11342,28 @@
         <f>(SUM(M31:M31)/5)*0.5</f>
         <v>0.5</v>
       </c>
-      <c r="O31" s="6" t="e">
+      <c r="O31" s="6">
         <f>L31+J31+F31</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P31" s="6" t="e">
+        <v>4.6466666666666665</v>
+      </c>
+      <c r="P31" s="6">
         <f>INT(O31*10)/10+IF(MOD(O31*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q31" s="1" t="e">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q31" s="1" t="str">
         <f>IF(O31&lt;3,3-O31,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="32" spans="1:17">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="26"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="5">
         <v>4</v>
       </c>
@@ -11157,17 +11371,25 @@
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="5" t="e">
+      <c r="G32" s="1">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I32" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="1"/>
+        <v>2.35</v>
+      </c>
+      <c r="K32" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L32" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9350000000000001</v>
       </c>
       <c r="M32" s="6">
         <v>8</v>
@@ -11176,39 +11398,47 @@
         <f>(SUM(M32:M32)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O32" s="6" t="e">
+      <c r="O32" s="6">
         <f>L32+J32+F32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P32" s="6" t="e">
+        <v>4.4850000000000003</v>
+      </c>
+      <c r="P32" s="6">
         <f>INT(O32*10)/10+IF(MOD(O32*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q32" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q32" s="1" t="str">
         <f>IF(O32&lt;3,3-O32,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="5"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="5">
+        <v>3</v>
+      </c>
       <c r="F33" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="5" t="e">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I33" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.25</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="6">
@@ -11220,28 +11450,28 @@
         <f>(SUM(M33:M33)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O33" s="6" t="e">
+      <c r="O33" s="6">
         <f>L33+J33+F33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P33" s="6" t="e">
+        <v>2.4</v>
+      </c>
+      <c r="P33" s="6">
         <f>INT(O33*10)/10+IF(MOD(O33*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q33" s="1" t="e">
+        <v>2.4</v>
+      </c>
+      <c r="Q33" s="1">
         <f>IF(O33&lt;3,3-O33,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25" t="s">
+      <c r="B34" s="28"/>
+      <c r="C34" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="26"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="5">
         <v>5</v>
       </c>
@@ -11249,17 +11479,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="5" t="e">
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I34" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K34" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="L34" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="M34" s="6">
         <v>10</v>
@@ -11268,72 +11506,82 @@
         <f>(SUM(M34:M34)/5)*0.5</f>
         <v>1</v>
       </c>
-      <c r="O34" s="6" t="e">
+      <c r="O34" s="6">
         <f>L34+J34+F34</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P34" s="6" t="e">
+        <v>4.6466666666666665</v>
+      </c>
+      <c r="P34" s="6">
         <f>INT(O34*10)/10+IF(MOD(O34*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q34" s="1" t="e">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q34" s="1" t="str">
         <f>IF(O34&lt;3,3-O34,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="25" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="5"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="5">
+        <v>0.9</v>
+      </c>
       <c r="F35" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="5" t="e">
+        <v>4.5000000000000005E-2</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I35" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J35" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K35" s="1">
+        <v>5</v>
+      </c>
       <c r="L35" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6">
         <f>(SUM(M35:M35)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O35" s="6" t="e">
+      <c r="O35" s="6">
         <f>L35+J35+F35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P35" s="6" t="e">
+        <v>4.711666666666666</v>
+      </c>
+      <c r="P35" s="6">
         <f>INT(O35*10)/10+IF(MOD(O35*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q35" s="1" t="e">
+        <v>4.7</v>
+      </c>
+      <c r="Q35" s="1" t="str">
         <f>IF(O35&lt;3,3-O35,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="26"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="5">
         <v>5</v>
       </c>
@@ -11341,17 +11589,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="5" t="e">
+      <c r="G36" s="1">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I36" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J36" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="K36" s="1">
+        <v>5</v>
+      </c>
       <c r="L36" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M36" s="6">
         <v>9</v>
@@ -11360,28 +11616,28 @@
         <f>(SUM(M36:M36)/5)*0.5</f>
         <v>0.9</v>
       </c>
-      <c r="O36" s="6" t="e">
+      <c r="O36" s="6">
         <f>L36+J36+F36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P36" s="6" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P36" s="6">
         <f>INT(O36*10)/10+IF(MOD(O36*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q36" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q36" s="1" t="str">
         <f>IF(O36&lt;3,3-O36,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="25" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="26"/>
+      <c r="D37" s="28"/>
       <c r="E37" s="5">
         <v>5</v>
       </c>
@@ -11389,17 +11645,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="5" t="e">
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J37" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="1"/>
+        <v>2.4499999999999997</v>
+      </c>
+      <c r="K37" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L37" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M37" s="6">
         <v>11</v>
@@ -11408,28 +11672,28 @@
         <f>(SUM(M37:M37)/5)*0.5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="O37" s="6" t="e">
+      <c r="O37" s="6">
         <f>L37+J37+F37</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P37" s="6" t="e">
+        <v>4.9049999999999994</v>
+      </c>
+      <c r="P37" s="6">
         <f>INT(O37*10)/10+IF(MOD(O37*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q37" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q37" s="1" t="str">
         <f>IF(O37&lt;3,3-O37,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="25" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="26"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="5">
         <v>4.3</v>
       </c>
@@ -11437,45 +11701,53 @@
         <f t="shared" si="0"/>
         <v>0.215</v>
       </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="5" t="e">
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K38" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K38" s="1">
+        <v>5</v>
+      </c>
       <c r="L38" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M38" s="6"/>
       <c r="N38" s="6">
         <f>(SUM(M38:M38)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O38" s="6" t="e">
+      <c r="O38" s="6">
         <f>L38+J38+F38</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P38" s="6" t="e">
+        <v>4.9483333333333333</v>
+      </c>
+      <c r="P38" s="6">
         <f>INT(O38*10)/10+IF(MOD(O38*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q38" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q38" s="1" t="str">
         <f>IF(O38&lt;3,3-O38,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="25" t="s">
+      <c r="B39" s="28"/>
+      <c r="C39" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="26"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="5">
         <v>4.5999999999999996</v>
       </c>
@@ -11483,17 +11755,25 @@
         <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="5" t="e">
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I39" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J39" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K39" s="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>4.7</v>
+      </c>
       <c r="L39" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.1150000000000002</v>
       </c>
       <c r="M39" s="6">
         <v>8</v>
@@ -11502,28 +11782,28 @@
         <f>(SUM(M39:M39)/5)*0.5</f>
         <v>0.8</v>
       </c>
-      <c r="O39" s="6" t="e">
+      <c r="O39" s="6">
         <f>L39+J39+F39</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P39" s="6" t="e">
+        <v>4.745000000000001</v>
+      </c>
+      <c r="P39" s="6">
         <f>INT(O39*10)/10+IF(MOD(O39*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q39" s="1" t="e">
+        <v>4.7</v>
+      </c>
+      <c r="Q39" s="1" t="str">
         <f>IF(O39&lt;3,3-O39,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="40" spans="1:17">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="25" t="s">
+      <c r="B40" s="28"/>
+      <c r="C40" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="26"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="13">
         <v>4.9000000000000004</v>
       </c>
@@ -11531,17 +11811,25 @@
         <f t="shared" si="0"/>
         <v>0.24500000000000002</v>
       </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="5" t="e">
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I40" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J40" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K40" s="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="K40" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L40" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.845</v>
       </c>
       <c r="M40" s="6">
         <v>10</v>
@@ -11550,28 +11838,28 @@
         <f>(SUM(M40:M40)/5)*0.5</f>
         <v>1</v>
       </c>
-      <c r="O40" s="6" t="e">
+      <c r="O40" s="6">
         <f>L40+J40+F40</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P40" s="6" t="e">
+        <v>4.49</v>
+      </c>
+      <c r="P40" s="6">
         <f>INT(O40*10)/10+IF(MOD(O40*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q40" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q40" s="1" t="str">
         <f>IF(O40&lt;3,3-O40,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="33"/>
+      <c r="C41" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="31"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="5">
         <v>4.9000000000000004</v>
       </c>
@@ -11579,17 +11867,25 @@
         <f t="shared" si="0"/>
         <v>0.24500000000000002</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="5" t="e">
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K41" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K41" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L41" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.845</v>
       </c>
       <c r="M41" s="6">
         <v>6</v>
@@ -11598,28 +11894,28 @@
         <f>(SUM(M41:M41)/5)*0.5</f>
         <v>0.6</v>
       </c>
-      <c r="O41" s="6" t="e">
+      <c r="O41" s="6">
         <f>L41+J41+F41</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P41" s="6" t="e">
+        <v>4.5066666666666668</v>
+      </c>
+      <c r="P41" s="6">
         <f>INT(O41*10)/10+IF(MOD(O41*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q41" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q41" s="1" t="str">
         <f>IF(O41&lt;3,3-O41,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="42" spans="1:17">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="26"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="5">
         <v>4.95</v>
       </c>
@@ -11627,17 +11923,25 @@
         <f t="shared" si="0"/>
         <v>0.24750000000000003</v>
       </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="5" t="e">
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J42" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K42" s="1"/>
+        <v>1.4666666666666668</v>
+      </c>
+      <c r="K42" s="1">
+        <v>5</v>
+      </c>
       <c r="L42" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M42" s="6">
         <v>3</v>
@@ -11646,28 +11950,28 @@
         <f>(SUM(M42:M42)/5)*0.5</f>
         <v>0.3</v>
       </c>
-      <c r="O42" s="6" t="e">
+      <c r="O42" s="6">
         <f>L42+J42+F42</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P42" s="6" t="e">
+        <v>3.9641666666666668</v>
+      </c>
+      <c r="P42" s="6">
         <f>INT(O42*10)/10+IF(MOD(O42*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q42" s="1" t="e">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="1" t="str">
         <f>IF(O42&lt;3,3-O42,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="25" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="26"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="5">
         <v>4</v>
       </c>
@@ -11675,45 +11979,53 @@
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="5" t="e">
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J43" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K43" s="1"/>
+        <v>1.4666666666666668</v>
+      </c>
+      <c r="K43" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L43" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.9350000000000001</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6">
         <f>(SUM(M43:M43)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O43" s="6" t="e">
+      <c r="O43" s="6">
         <f>L43+J43+F43</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P43" s="6" t="e">
+        <v>3.601666666666667</v>
+      </c>
+      <c r="P43" s="6">
         <f>INT(O43*10)/10+IF(MOD(O43*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q43" s="1" t="e">
+        <v>3.6</v>
+      </c>
+      <c r="Q43" s="1" t="str">
         <f>IF(O43&lt;3,3-O43,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="25" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="26"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="5">
         <v>5</v>
       </c>
@@ -11721,17 +12033,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="5" t="e">
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>5</v>
+      </c>
+      <c r="I44" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J44" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K44" s="1"/>
+        <v>2.4499999999999997</v>
+      </c>
+      <c r="K44" s="1">
+        <v>5</v>
+      </c>
       <c r="L44" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M44" s="6">
         <v>9</v>
@@ -11740,28 +12060,28 @@
         <f>(SUM(M44:M44)/5)*0.5</f>
         <v>0.9</v>
       </c>
-      <c r="O44" s="6" t="e">
+      <c r="O44" s="6">
         <f>L44+J44+F44</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P44" s="6" t="e">
+        <v>4.9499999999999993</v>
+      </c>
+      <c r="P44" s="6">
         <f>INT(O44*10)/10+IF(MOD(O44*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q44" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q44" s="1" t="str">
         <f>IF(O44&lt;3,3-O44,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="25" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="26"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="5">
         <v>5</v>
       </c>
@@ -11769,17 +12089,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="5" t="e">
+      <c r="G45" s="1">
+        <v>5</v>
+      </c>
+      <c r="H45" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K45" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K45" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L45" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M45" s="6">
         <v>11</v>
@@ -11788,28 +12116,28 @@
         <f>(SUM(M45:M45)/5)*0.5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="O45" s="6" t="e">
+      <c r="O45" s="6">
         <f>L45+J45+F45</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P45" s="6" t="e">
+        <v>4.9383333333333335</v>
+      </c>
+      <c r="P45" s="6">
         <f>INT(O45*10)/10+IF(MOD(O45*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q45" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q45" s="1" t="str">
         <f>IF(O45&lt;3,3-O45,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="25" t="s">
+      <c r="B46" s="28"/>
+      <c r="C46" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="26"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="5">
         <v>3.3</v>
       </c>
@@ -11817,17 +12145,25 @@
         <f t="shared" si="0"/>
         <v>0.16500000000000001</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="5" t="e">
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I46" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J46" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K46" s="1"/>
+        <v>2.3666666666666667</v>
+      </c>
+      <c r="K46" s="1">
+        <v>3.5</v>
+      </c>
       <c r="L46" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="M46" s="6">
         <v>6</v>
@@ -11836,28 +12172,28 @@
         <f>(SUM(M46:M46)/5)*0.5</f>
         <v>0.6</v>
       </c>
-      <c r="O46" s="6" t="e">
+      <c r="O46" s="6">
         <f>L46+J46+F46</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P46" s="6" t="e">
+        <v>4.1066666666666665</v>
+      </c>
+      <c r="P46" s="6">
         <f>INT(O46*10)/10+IF(MOD(O46*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q46" s="1" t="e">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q46" s="1" t="str">
         <f>IF(O46&lt;3,3-O46,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="25" t="s">
+      <c r="B47" s="28"/>
+      <c r="C47" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="26"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="5">
         <v>4.4000000000000004</v>
       </c>
@@ -11865,45 +12201,53 @@
         <f t="shared" si="0"/>
         <v>0.22000000000000003</v>
       </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="5" t="e">
+      <c r="G47" s="1">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K47" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K47" s="1">
+        <v>4</v>
+      </c>
       <c r="L47" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M47" s="6"/>
       <c r="N47" s="6">
         <f>(SUM(M47:M47)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O47" s="6" t="e">
+      <c r="O47" s="6">
         <f>L47+J47+F47</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P47" s="6" t="e">
+        <v>4.503333333333333</v>
+      </c>
+      <c r="P47" s="6">
         <f>INT(O47*10)/10+IF(MOD(O47*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q47" s="1" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="Q47" s="1" t="str">
         <f>IF(O47&lt;3,3-O47,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30" t="s">
+      <c r="B48" s="33"/>
+      <c r="C48" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="31"/>
+      <c r="D48" s="33"/>
       <c r="E48" s="5">
         <v>4.3</v>
       </c>
@@ -11911,45 +12255,53 @@
         <f t="shared" si="0"/>
         <v>0.215</v>
       </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="5" t="e">
+      <c r="G48" s="1">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5</v>
+      </c>
+      <c r="I48" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J48" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K48" s="1"/>
+        <v>2.4499999999999997</v>
+      </c>
+      <c r="K48" s="1">
+        <v>3.7</v>
+      </c>
       <c r="L48" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.665</v>
       </c>
       <c r="M48" s="6"/>
       <c r="N48" s="6">
         <f>(SUM(M48:M48)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O48" s="6" t="e">
+      <c r="O48" s="6">
         <f>L48+J48+F48</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P48" s="6" t="e">
+        <v>4.33</v>
+      </c>
+      <c r="P48" s="6">
         <f>INT(O48*10)/10+IF(MOD(O48*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q48" s="1" t="e">
+        <v>4.3</v>
+      </c>
+      <c r="Q48" s="1" t="str">
         <f>IF(O48&lt;3,3-O48,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="49" spans="1:17">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30" t="s">
+      <c r="B49" s="33"/>
+      <c r="C49" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="31"/>
+      <c r="D49" s="33"/>
       <c r="E49" s="5">
         <v>4.9000000000000004</v>
       </c>
@@ -11957,45 +12309,53 @@
         <f t="shared" si="0"/>
         <v>0.24500000000000002</v>
       </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="5" t="e">
+      <c r="G49" s="1">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I49" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="J49" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K49" s="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="K49" s="1">
+        <v>3.5</v>
+      </c>
       <c r="L49" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6">
         <f>(SUM(M49:M49)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O49" s="6" t="e">
+      <c r="O49" s="6">
         <f>L49+J49+F49</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P49" s="6" t="e">
+        <v>4.07</v>
+      </c>
+      <c r="P49" s="6">
         <f>INT(O49*10)/10+IF(MOD(O49*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q49" s="1" t="e">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q49" s="1" t="str">
         <f>IF(O49&lt;3,3-O49,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="50" spans="1:17">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30" t="s">
+      <c r="B50" s="33"/>
+      <c r="C50" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="31"/>
+      <c r="D50" s="33"/>
       <c r="E50" s="5">
         <v>5</v>
       </c>
@@ -12003,17 +12363,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="5" t="e">
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K50" s="1"/>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="K50" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L50" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="M50" s="6">
         <v>11</v>
@@ -12022,28 +12390,28 @@
         <f>(SUM(M50:M50)/5)*0.5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="O50" s="6" t="e">
+      <c r="O50" s="6">
         <f>L50+J50+F50</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P50" s="6" t="e">
+        <v>4.9383333333333335</v>
+      </c>
+      <c r="P50" s="6">
         <f>INT(O50*10)/10+IF(MOD(O50*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q50" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q50" s="1" t="str">
         <f>IF(O50&lt;3,3-O50,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="51" spans="1:17">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30" t="s">
+      <c r="B51" s="33"/>
+      <c r="C51" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="31"/>
+      <c r="D51" s="33"/>
       <c r="E51" s="5">
         <v>3.7</v>
       </c>
@@ -12051,17 +12419,25 @@
         <f t="shared" si="0"/>
         <v>0.18500000000000003</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="5" t="e">
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4</v>
+      </c>
+      <c r="I51" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J51" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K51" s="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3.9</v>
+      </c>
       <c r="L51" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="M51" s="6">
         <v>1</v>
@@ -12070,28 +12446,28 @@
         <f>(SUM(M51:M51)/5)*0.5</f>
         <v>0.1</v>
       </c>
-      <c r="O51" s="6" t="e">
+      <c r="O51" s="6">
         <f>L51+J51+F51</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P51" s="6" t="e">
+        <v>4.1899999999999995</v>
+      </c>
+      <c r="P51" s="6">
         <f>INT(O51*10)/10+IF(MOD(O51*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q51" s="1" t="e">
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="Q51" s="1" t="str">
         <f>IF(O51&lt;3,3-O51,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="52" spans="1:17">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="33"/>
+      <c r="C52" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="31"/>
+      <c r="D52" s="33"/>
       <c r="E52" s="5">
         <v>4.95</v>
       </c>
@@ -12099,34 +12475,42 @@
         <f t="shared" si="0"/>
         <v>0.24750000000000003</v>
       </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="5" t="e">
+      <c r="G52" s="1">
+        <v>5</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J52" s="5">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K52" s="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+      <c r="K52" s="1">
+        <v>5</v>
+      </c>
       <c r="L52" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6">
         <f>(SUM(M52:M52)/5)*0.5</f>
         <v>0</v>
       </c>
-      <c r="O52" s="6" t="e">
+      <c r="O52" s="6">
         <f>L52+J52+F52</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P52" s="6" t="e">
+        <v>4.9141666666666657</v>
+      </c>
+      <c r="P52" s="6">
         <f>INT(O52*10)/10+IF(MOD(O52*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q52" s="1" t="e">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q52" s="1" t="str">
         <f>IF(O52&lt;3,3-O52,"No aplica")</f>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
   </sheetData>
